--- a/ResourcesTH/OutletExcel.xlsx
+++ b/ResourcesTH/OutletExcel.xlsx
@@ -5,21 +5,21 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\Resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesTH\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="6930"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="5480"/>
   </bookViews>
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" concurrentManualCount="8"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="832" uniqueCount="149">
   <si>
     <t>Outlet Code*</t>
   </si>
@@ -219,49 +219,40 @@
     <t>Credit Day Limit</t>
   </si>
   <si>
+    <t>Days Action</t>
+  </si>
+  <si>
     <t>Credit Amount Limit</t>
   </si>
   <si>
+    <t>Amount Action</t>
+  </si>
+  <si>
     <t>Owner Name*</t>
   </si>
   <si>
     <t>Owner Name Secondary*</t>
   </si>
   <si>
-    <t>C0000000006</t>
-  </si>
-  <si>
-    <t>KHAADI</t>
-  </si>
-  <si>
-    <t>HBKD</t>
-  </si>
-  <si>
-    <t>50200411</t>
-  </si>
-  <si>
-    <t>STMI PASIG MAG</t>
-  </si>
-  <si>
-    <t>657281537678</t>
-  </si>
-  <si>
-    <t>DHA Section</t>
-  </si>
-  <si>
-    <t>2025-07-08</t>
+    <t>Customer Class*</t>
+  </si>
+  <si>
+    <t>Branch Code</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>50000598</t>
+  </si>
+  <si>
+    <t>บริษัท ศุภaมิตร แอล วี จำกัด</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t/>
-  </si>
-  <si>
-    <t>C01768C14865</t>
-  </si>
-  <si>
-    <t>002001D01206D10536D32181D57558</t>
+    <t>002002002002002002002002002002</t>
   </si>
   <si>
     <t>001001</t>
@@ -273,52 +264,208 @@
     <t>A</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>U</t>
+  </si>
+  <si>
+    <t>CA82</t>
+  </si>
+  <si>
+    <t>06001001</t>
+  </si>
+  <si>
+    <t>5401001001</t>
+  </si>
+  <si>
+    <t>123</t>
+  </si>
+  <si>
+    <t>CAP1</t>
+  </si>
+  <si>
+    <t>CA33</t>
+  </si>
+  <si>
+    <t>CA41</t>
+  </si>
+  <si>
+    <t>CA10</t>
+  </si>
+  <si>
+    <t>CA901</t>
+  </si>
+  <si>
+    <t>CA11</t>
+  </si>
+  <si>
+    <t>CA12</t>
+  </si>
+  <si>
+    <t>CA81</t>
+  </si>
+  <si>
+    <t>C10002</t>
+  </si>
+  <si>
     <t>0001</t>
   </si>
   <si>
-    <t>2025-06-11</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>NA01</t>
-  </si>
-  <si>
-    <t>41241</t>
-  </si>
-  <si>
-    <t>4124142</t>
-  </si>
-  <si>
-    <t>003</t>
-  </si>
-  <si>
-    <t>07001</t>
-  </si>
-  <si>
-    <t>07621257487</t>
-  </si>
-  <si>
-    <t>0323232323232323</t>
-  </si>
-  <si>
-    <t>45787412121101001</t>
-  </si>
-  <si>
-    <t>7816425241244</t>
-  </si>
-  <si>
-    <t>NA002</t>
-  </si>
-  <si>
-    <t>HJKAsiq2</t>
-  </si>
-  <si>
-    <t>NA</t>
+    <t>0101</t>
+  </si>
+  <si>
+    <t>OPG1</t>
+  </si>
+  <si>
+    <t>CA45</t>
+  </si>
+  <si>
+    <t>CAT4</t>
+  </si>
+  <si>
+    <t>CA13</t>
+  </si>
+  <si>
+    <t>Thai00000008</t>
+  </si>
+  <si>
+    <t>Central Pattaya</t>
+  </si>
+  <si>
+    <t>2025-07-31</t>
+  </si>
+  <si>
+    <t>wde</t>
+  </si>
+  <si>
+    <t>CA31</t>
+  </si>
+  <si>
+    <t>asd</t>
+  </si>
+  <si>
+    <t>Owner4</t>
+  </si>
+  <si>
+    <t>Owner5</t>
+  </si>
+  <si>
+    <t>Owner6</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL56F1F</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCA57D</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB1BA10</t>
+  </si>
+  <si>
+    <t>branch123</t>
+  </si>
+  <si>
+    <t>C0000000234</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL041E4</t>
+  </si>
+  <si>
+    <t>03232031600</t>
+  </si>
+  <si>
+    <t>C0000000235</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL70CEC</t>
+  </si>
+  <si>
+    <t>03234448600</t>
+  </si>
+  <si>
+    <t>C0000000236</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD5484</t>
+  </si>
+  <si>
+    <t>03526890700</t>
+  </si>
+  <si>
+    <t>C0000000237</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL519C1</t>
+  </si>
+  <si>
+    <t>03528627200</t>
+  </si>
+  <si>
+    <t>C0000000238</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAA1FE</t>
+  </si>
+  <si>
+    <t>03530182800</t>
+  </si>
+  <si>
+    <t>C0000000239</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB8930</t>
+  </si>
+  <si>
+    <t>03463983700</t>
+  </si>
+  <si>
+    <t>C0000000240</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6B3E9</t>
+  </si>
+  <si>
+    <t>03468092800</t>
+  </si>
+  <si>
+    <t>C0000000241</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3F1A2</t>
+  </si>
+  <si>
+    <t>03474955300</t>
+  </si>
+  <si>
+    <t>C0000000242</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL12771</t>
+  </si>
+  <si>
+    <t>03765150900</t>
+  </si>
+  <si>
+    <t>C0000000243</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDB972</t>
+  </si>
+  <si>
+    <t>03767589300</t>
+  </si>
+  <si>
+    <t>C0000000244</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL27B7E</t>
+  </si>
+  <si>
+    <t>03769260700</t>
+  </si>
+  <si>
+    <t>CA51</t>
   </si>
 </sst>
 </file>
@@ -642,81 +789,28 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BQ2"/>
+  <dimension ref="A1:BU12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="17.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.90625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="18.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.6328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="17.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="32.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" style="3" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="8.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="12.7265625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="11.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="5.81640625" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.54296875" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="13.6328125" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="15" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.54296875" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.08984375" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="8.36328125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="21.453125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="22.08984375" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="20.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="10" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="42" width="9" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="43" width="6.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="44" max="44" width="17.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="45" max="45" width="11.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="46" max="46" width="16.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="47" max="47" width="5.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="48" max="48" width="11.7265625" style="1" bestFit="1" customWidth="1"/>
-    <col min="49" max="49" width="10.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="50" max="50" width="12.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="51" max="51" width="15" style="1" bestFit="1" customWidth="1"/>
-    <col min="52" max="52" width="13.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="53" max="53" width="18.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="54" max="54" width="17" style="1" bestFit="1" customWidth="1"/>
-    <col min="55" max="55" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="56" max="56" width="17.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="57" max="57" width="4.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="58" max="58" width="11.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="59" max="59" width="7.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="60" max="60" width="13.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="61" max="61" width="11.453125" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="8" width="8" style="1"/>
+    <col min="11" max="15" width="8" style="1"/>
+    <col min="16" max="17" width="8" style="3"/>
+    <col min="18" max="20" width="8" style="1"/>
+    <col min="22" max="22" width="8" style="1"/>
+    <col min="24" max="24" width="8" style="1"/>
+    <col min="33" max="33" width="8" style="2"/>
+    <col min="34" max="34" width="8" style="1"/>
+    <col min="38" max="38" width="8" style="1"/>
+    <col min="40" max="61" width="8" style="1"/>
     <col min="62" max="62" width="12.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="63" max="63" width="10.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="64" max="64" width="14.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="65" max="65" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="66" max="66" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="67" max="67" width="17.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="68" max="68" width="12.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="69" max="69" width="22.1796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="63" max="65" width="8" style="1"/>
+    <col min="66" max="66" width="8" style="2"/>
+    <col min="68" max="68" width="8" style="3"/>
+    <col min="70" max="71" width="8" style="1"/>
+    <col min="72" max="72" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -915,223 +1009,2457 @@
       <c r="BN1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="BO1" s="3" t="s">
+      <c r="BO1" t="s">
         <v>66</v>
       </c>
-      <c r="BP1" s="1" t="s">
+      <c r="BP1" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="BQ1" s="1" t="s">
+      <c r="BQ1" t="s">
         <v>68</v>
       </c>
+      <c r="BR1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="BS1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="BT1" t="s">
+        <v>71</v>
+      </c>
+      <c r="BU1" t="s">
+        <v>72</v>
+      </c>
     </row>
-    <row r="2" spans="1:69" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:73" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>69</v>
+        <v>115</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>70</v>
+        <v>116</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>74</v>
+        <v>102</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>75</v>
+        <v>103</v>
       </c>
       <c r="I2" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="J2" t="s">
+        <v>76</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="P2" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q2" s="3">
+        <v>24.744137018150173</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="L2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="N2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="T2" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U2" t="s">
         <v>80</v>
       </c>
-      <c r="P2" s="3">
-        <v>10.65</v>
-      </c>
-      <c r="Q2" s="3">
-        <v>12.36</v>
-      </c>
-      <c r="R2" s="1" t="s">
+      <c r="V2" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W2" t="s">
+        <v>104</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA2" t="s">
         <v>81</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="AB2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE2" t="s">
         <v>82</v>
       </c>
-      <c r="T2" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="U2" t="s">
-        <v>83</v>
-      </c>
-      <c r="V2" s="1" t="s">
+      <c r="AF2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG2" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL2" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR2" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT2" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU2" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="W2" t="s">
+      <c r="AV2" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="X2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>78</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>85</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>86</v>
-      </c>
-      <c r="AD2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AE2" t="s">
-        <v>87</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AG2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AH2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AI2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AJ2" t="s">
-        <v>77</v>
-      </c>
-      <c r="AK2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AL2" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="AM2" t="s">
-        <v>78</v>
-      </c>
-      <c r="AN2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AO2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AP2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AQ2" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="AR2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AS2" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="AT2" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="AU2" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="AV2" s="1" t="s">
-        <v>78</v>
-      </c>
       <c r="AW2" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>78</v>
+        <v>73</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="BG2" s="1" t="s">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="BH2" s="1" t="s">
         <v>88</v>
       </c>
       <c r="BI2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ2" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK2" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL2" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM2" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN2" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP2" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ2" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS2" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BT2" t="s">
+        <v>92</v>
+      </c>
+      <c r="BU2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I3" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" t="s">
+        <v>76</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P3" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q3" s="3">
+        <v>24.992586546661226</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U3" t="s">
+        <v>80</v>
+      </c>
+      <c r="V3" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W3" t="s">
+        <v>104</v>
+      </c>
+      <c r="X3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y3" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL3" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AQ3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS3" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT3" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU3" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV3" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="AZ3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD3" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF3" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG3" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH3" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BI3" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ3" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK3" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL3" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM3" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN3" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP3" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ3" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BS3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT3" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU3" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="4" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A4" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I4" t="s">
+        <v>73</v>
+      </c>
+      <c r="J4" t="s">
+        <v>76</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N4" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P4" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q4" s="3">
+        <v>24.715874855094288</v>
+      </c>
+      <c r="R4" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U4" t="s">
+        <v>80</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W4" t="s">
+        <v>104</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y4" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG4" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AT4" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU4" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV4" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY4" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="AZ4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD4" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF4" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG4" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH4" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="BJ2" s="1" t="s">
+      <c r="BI4" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="BK2" s="1" t="s">
+      <c r="BJ4" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK4" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL4" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM4" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN4" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO4" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP4" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ4" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BS4" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BT4" t="s">
+        <v>93</v>
+      </c>
+      <c r="BU4" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I5" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" t="s">
+        <v>76</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P5" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q5" s="3">
+        <v>24.531175233599669</v>
+      </c>
+      <c r="R5" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U5" t="s">
+        <v>80</v>
+      </c>
+      <c r="V5" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W5" t="s">
+        <v>104</v>
+      </c>
+      <c r="X5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y5" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL5" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY5" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AZ5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD5" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF5" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG5" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH5" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="BL2" s="1" t="s">
+      <c r="BI5" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ5" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK5" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL5" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM5" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN5" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO5" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP5" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ5" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS5" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BT5" t="s">
+        <v>92</v>
+      </c>
+      <c r="BU5" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I6" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" t="s">
+        <v>76</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N6" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P6" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q6" s="3">
+        <v>24.182178250892004</v>
+      </c>
+      <c r="R6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="BM2" s="1" t="s">
+      <c r="S6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U6" t="s">
+        <v>80</v>
+      </c>
+      <c r="V6" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W6" t="s">
+        <v>104</v>
+      </c>
+      <c r="X6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y6" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z6" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA6" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG6" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL6" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AQ6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS6" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT6" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY6" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="AZ6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD6" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE6" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF6" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BG6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH6" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BI6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ6" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK6" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL6" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM6" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN6" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO6" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP6" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ6" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BS6" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT6" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU6" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A7" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" t="s">
+        <v>76</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P7" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q7" s="3">
+        <v>24.304628853480253</v>
+      </c>
+      <c r="R7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="BO2" s="3" t="s">
+      <c r="S7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U7" t="s">
+        <v>80</v>
+      </c>
+      <c r="V7" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W7" t="s">
+        <v>104</v>
+      </c>
+      <c r="X7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y7" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA7" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG7" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL7" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AT7" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU7" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV7" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY7" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="AZ7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD7" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE7" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF7" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG7" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BI7" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ7" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL7" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN7" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO7" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP7" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ7" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BS7" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BT7" t="s">
+        <v>93</v>
+      </c>
+      <c r="BU7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="8" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A8" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I8" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" t="s">
+        <v>76</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P8" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q8" s="3">
+        <v>24.069504861386111</v>
+      </c>
+      <c r="R8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="BP2" s="1" t="s">
+      <c r="S8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U8" t="s">
+        <v>80</v>
+      </c>
+      <c r="V8" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W8" t="s">
+        <v>104</v>
+      </c>
+      <c r="X8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG8" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT8" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU8" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV8" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY8" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="AZ8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD8" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE8" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF8" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG8" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH8" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BI8" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ8" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK8" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL8" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="BQ2" s="1" t="s">
+      <c r="BM8" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN8" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO8" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP8" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ8" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS8" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BT8" t="s">
+        <v>92</v>
+      </c>
+      <c r="BU8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="9" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A9" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I9" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" t="s">
+        <v>76</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P9" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q9" s="3">
+        <v>24.724138606820283</v>
+      </c>
+      <c r="R9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U9" t="s">
+        <v>80</v>
+      </c>
+      <c r="V9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W9" t="s">
+        <v>104</v>
+      </c>
+      <c r="X9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y9" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z9" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA9" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG9" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL9" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AQ9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS9" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT9" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU9" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV9" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY9" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="AZ9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD9" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE9" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG9" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH9" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BI9" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ9" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK9" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL9" s="1" t="s">
         <v>98</v>
+      </c>
+      <c r="BM9" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN9" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO9" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP9" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ9" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BS9" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT9" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU9" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A10" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I10" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" t="s">
+        <v>76</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P10" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q10" s="3">
+        <v>24.944937663115809</v>
+      </c>
+      <c r="R10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U10" t="s">
+        <v>80</v>
+      </c>
+      <c r="V10" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W10" t="s">
+        <v>104</v>
+      </c>
+      <c r="X10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y10" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA10" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG10" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL10" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AP10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AQ10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AT10" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="AU10" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV10" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="AZ10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD10" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF10" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH10" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BI10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ10" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK10" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL10" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM10" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN10" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO10" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP10" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ10" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BS10" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="BT10" t="s">
+        <v>93</v>
+      </c>
+      <c r="BU10" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="11" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I11" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" t="s">
+        <v>76</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N11" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P11" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q11" s="3">
+        <v>24.920798962850217</v>
+      </c>
+      <c r="R11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U11" t="s">
+        <v>80</v>
+      </c>
+      <c r="V11" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W11" t="s">
+        <v>104</v>
+      </c>
+      <c r="X11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL11" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AT11" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU11" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV11" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY11" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="AZ11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD11" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF11" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG11" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="BH11" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="BI11" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="BJ11" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM11" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN11" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO11" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP11" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ11" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BS11" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="BT11" t="s">
+        <v>92</v>
+      </c>
+      <c r="BU11" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="12" spans="1:73" x14ac:dyDescent="0.35">
+      <c r="A12" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="I12" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" t="s">
+        <v>76</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="N12" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="O12" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="P12" s="3">
+        <v>12.12</v>
+      </c>
+      <c r="Q12" s="3">
+        <v>24.961442951803107</v>
+      </c>
+      <c r="R12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="S12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="T12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="U12" t="s">
+        <v>80</v>
+      </c>
+      <c r="V12" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="W12" t="s">
+        <v>104</v>
+      </c>
+      <c r="X12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>73</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>104</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>81</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>82</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AG12" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AH12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AL12" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>76</v>
+      </c>
+      <c r="AN12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AO12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AP12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AQ12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AR12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AS12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="AT12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="AU12" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="AV12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="AW12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AX12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY12" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="AZ12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BA12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BB12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BC12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BD12" s="1" t="s">
+        <v>73</v>
+      </c>
+      <c r="BE12" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF12" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="BG12" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="BH12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="BI12" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="BJ12" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BK12" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="BL12" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="BM12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="BN12" s="2">
+        <v>10</v>
+      </c>
+      <c r="BO12" t="s">
+        <v>80</v>
+      </c>
+      <c r="BP12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="BQ12" t="s">
+        <v>80</v>
+      </c>
+      <c r="BR12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BS12" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="BT12" t="s">
+        <v>101</v>
+      </c>
+      <c r="BU12" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
